--- a/product_selector_out/STM32L100 value line.xlsx
+++ b/product_selector_out/STM32L100 value line.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3190,7 +3196,7 @@
       </c>
       <c r="AW18" s="4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX18" s="4" t="inlineStr">
@@ -4099,9 +4105,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -4426,9 +4432,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -4753,9 +4759,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -5080,9 +5086,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -5407,9 +5413,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -5734,9 +5740,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -6061,9 +6067,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -6162,7 +6168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6193,7 +6199,160 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L100C6-A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L100C6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L100RB-A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L100R8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L100RB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L100R8-A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L100RC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L100 value line.xlsx
+++ b/product_selector_out/STM32L100 value line.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32L100 value line.xlsx
+++ b/product_selector_out/STM32L100 value line.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM18"/>
+  <dimension ref="A1:BN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.00390625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
@@ -3276,12 +3313,17 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3302,16 +3344,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3324,6 +3364,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3343,7 +3384,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3367,7 +3410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM18"/>
+  <dimension ref="A1:BN18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3435,6 +3478,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3768,6 +3812,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -3863,6 +3912,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4185,7 +4235,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4512,7 +4567,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4839,7 +4899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5166,7 +5231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5493,7 +5563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5820,7 +5895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6147,7 +6227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6155,8 +6240,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
